--- a/短時間勤務者_採用KPIダッシュボード.xlsx
+++ b/短時間勤務者_採用KPIダッシュボード.xlsx
@@ -98,8 +98,14 @@
     </font>
     <font>
       <name val="Meiryo"/>
+      <b val="1"/>
       <color rgb="000000FF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo"/>
@@ -111,11 +117,6 @@
       <b val="1"/>
       <color rgb="002E5496"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Meiryo"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo"/>
@@ -158,12 +159,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00808080"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00808080"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -204,16 +205,34 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,16 +241,10 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -247,8 +260,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -439,12 +455,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'KPIダッシュボード'!$B$6:$B$11</f>
+              <f>'KPIダッシュボード'!$B$11:$B$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'KPIダッシュボード'!$D$6:$D$11</f>
+              <f>'KPIダッシュボード'!$D$11:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -511,7 +527,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'KPIダッシュボード'!C21</f>
+              <f>'KPIダッシュボード'!C27</f>
             </strRef>
           </tx>
           <spPr>
@@ -521,12 +537,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'KPIダッシュボード'!$B$22:$B$27</f>
+              <f>'KPIダッシュボード'!$B$28:$B$33</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'KPIダッシュボード'!$C$22:$C$27</f>
+              <f>'KPIダッシュボード'!$C$28:$C$33</f>
             </numRef>
           </val>
         </ser>
@@ -1175,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H40"/>
+  <dimension ref="B1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1205,747 +1221,942 @@
     <row r="4" ht="22" customHeight="1">
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>①  採用ファネル：目標 vs 実績（累計）</t>
+          <t>◎  目標設定 ─ 黄色セルに入力（採用目標から各段階の目標を自動逆算）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="4" t="inlineStr">
         <is>
+          <t>採用目標（承諾・人）</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>NRT(成田)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>CTS(千歳)</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="H5" s="7">
+        <f>D5+F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>歩留まり前提</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>書類通過率</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>面接設定率</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>面接実施率</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>内定率</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>承諾率</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>（応募→承諾）</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>①  採用ファネル：目標 vs 実績（累計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>目標</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>目標(逆算)</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
         <is>
           <t>実績(累計)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>達成率</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>前日</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>前日比</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="5" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>応募数</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D6" s="7">
+      <c r="C11" s="12">
+        <f>ROUNDUP(C12/$C$7,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="13">
         <f>COUNTA(応募者データ!$E$3:$E$502)</f>
         <v/>
       </c>
-      <c r="E6" s="8">
-        <f>IFERROR(D6/C6,"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="7">
+      <c r="E11" s="14">
+        <f>IFERROR(D11/C11,"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="13">
         <f>IFERROR(LOOKUP(1E+100,日次レポート!B$4:B$200),0)</f>
         <v/>
       </c>
-      <c r="G6" s="9">
-        <f>D6-F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="G11" s="15">
+        <f>D11-F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>書類通過</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D7" s="7">
+      <c r="C12" s="12">
+        <f>ROUNDUP(C13/$D$7,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="13">
         <f>COUNTIF(応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E7" s="8">
-        <f>IFERROR(D7/C7,"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="7">
+      <c r="E12" s="14">
+        <f>IFERROR(D12/C12,"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="13">
         <f>IFERROR(LOOKUP(1E+100,日次レポート!C$4:C$200),0)</f>
         <v/>
       </c>
-      <c r="G7" s="9">
-        <f>D7-F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="5" t="inlineStr">
+      <c r="G12" s="15">
+        <f>D12-F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>面接設定</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C13" s="12">
+        <f>ROUNDUP(C14/$E$7,0)</f>
+        <v/>
+      </c>
+      <c r="D13" s="13">
         <f>COUNTIF(応募者データ!$K$3:$K$502,"面接調整中")+COUNTIF(応募者データ!$K$3:$K$502,"面接日確定")+COUNTIF(応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="E8" s="8">
-        <f>IFERROR(D8/C8,"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="7">
+      <c r="E13" s="14">
+        <f>IFERROR(D13/C13,"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="13">
         <f>IFERROR(LOOKUP(1E+100,日次レポート!D$4:D$200),0)</f>
         <v/>
       </c>
-      <c r="G8" s="9">
-        <f>D8-F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>面接実施</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D9" s="7">
-        <f>COUNTIF(応募者データ!$K$3:$K$502,"面接実施済み")</f>
-        <v/>
-      </c>
-      <c r="E9" s="8">
-        <f>IFERROR(D9/C9,"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="7">
-        <f>IFERROR(LOOKUP(1E+100,日次レポート!E$4:E$200),0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="9">
-        <f>D9-F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>内定</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D10" s="7">
-        <f>COUNTIF(応募者データ!$M$3:$M$502,"採用")+COUNTIF(応募者データ!$M$3:$M$502,"入社予定")+COUNTIF(応募者データ!$M$3:$M$502,"採用辞退")+COUNTIF(応募者データ!$M$3:$M$502,"入社辞退")</f>
-        <v/>
-      </c>
-      <c r="E10" s="8">
-        <f>IFERROR(D10/C10,"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="7">
-        <f>IFERROR(LOOKUP(1E+100,日次レポート!F$4:F$200),0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="9">
-        <f>D10-F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>承諾</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="D11" s="7">
-        <f>COUNTIF(応募者データ!$M$3:$M$502,"採用")+COUNTIF(応募者データ!$M$3:$M$502,"入社予定")</f>
-        <v/>
-      </c>
-      <c r="E11" s="8">
-        <f>IFERROR(D11/C11,"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="7">
-        <f>IFERROR(LOOKUP(1E+100,日次レポート!G$4:G$200),0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="9">
-        <f>D11-F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>②  転換率（歩留まり）</t>
-        </is>
+      <c r="G13" s="15">
+        <f>D13-F13</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>面接実施</t>
+        </is>
+      </c>
+      <c r="C14" s="12">
+        <f>ROUNDUP(C15/$F$7,0)</f>
+        <v/>
+      </c>
+      <c r="D14" s="13">
+        <f>COUNTIF(応募者データ!$K$3:$K$502,"面接実施済み")</f>
+        <v/>
+      </c>
+      <c r="E14" s="14">
+        <f>IFERROR(D14/C14,"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="13">
+        <f>IFERROR(LOOKUP(1E+100,日次レポート!E$4:E$200),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="15">
+        <f>D14-F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>内定</t>
+        </is>
+      </c>
+      <c r="C15" s="12">
+        <f>ROUNDUP(C16/$G$7,0)</f>
+        <v/>
+      </c>
+      <c r="D15" s="13">
+        <f>COUNTIF(応募者データ!$M$3:$M$502,"採用")+COUNTIF(応募者データ!$M$3:$M$502,"入社予定")+COUNTIF(応募者データ!$M$3:$M$502,"採用辞退")+COUNTIF(応募者データ!$M$3:$M$502,"入社辞退")</f>
+        <v/>
+      </c>
+      <c r="E15" s="14">
+        <f>IFERROR(D15/C15,"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="13">
+        <f>IFERROR(LOOKUP(1E+100,日次レポート!F$4:F$200),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="15">
+        <f>D15-F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>承諾</t>
+        </is>
+      </c>
+      <c r="C16" s="12">
+        <f>$H$5</f>
+        <v/>
+      </c>
+      <c r="D16" s="13">
+        <f>COUNTIF(応募者データ!$M$3:$M$502,"採用")+COUNTIF(応募者データ!$M$3:$M$502,"入社予定")</f>
+        <v/>
+      </c>
+      <c r="E16" s="14">
+        <f>IFERROR(D16/C16,"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="13">
+        <f>IFERROR(LOOKUP(1E+100,日次レポート!G$4:G$200),0)</f>
+        <v/>
+      </c>
+      <c r="G16" s="15">
+        <f>D16-F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>②  転換率（歩留まり）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
           <t>指標</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>値</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>計算式・定義</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>書類通過率</t>
         </is>
       </c>
-      <c r="C15" s="10">
-        <f>IFERROR(D7/D6,"")</f>
-        <v/>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="C20" s="16">
+        <f>IFERROR(D12/D11,"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>書類通過 ÷ 応募数</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-    </row>
-    <row r="16">
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>面接設定率</t>
-        </is>
-      </c>
-      <c r="C16" s="10">
-        <f>IFERROR(D8/D7,"")</f>
-        <v/>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>面接設定 ÷ 書類通過</t>
-        </is>
-      </c>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>面接実施率</t>
-        </is>
-      </c>
-      <c r="C17" s="10">
-        <f>IFERROR(D9/D8,"")</f>
-        <v/>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>面接実施 ÷ 面接設定</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>内定率</t>
-        </is>
-      </c>
-      <c r="C18" s="10">
-        <f>IFERROR(D10/D9,"")</f>
-        <v/>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>内定 ÷ 面接実施</t>
-        </is>
-      </c>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>承諾率</t>
-        </is>
-      </c>
-      <c r="C19" s="10">
-        <f>IFERROR(D11/D10,"")</f>
-        <v/>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>承諾 ÷ 内定</t>
-        </is>
-      </c>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>③  媒体別 実績</t>
-        </is>
-      </c>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>面接設定率</t>
+        </is>
+      </c>
+      <c r="C21" s="16">
+        <f>IFERROR(D13/D12,"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>面接設定 ÷ 書類通過</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>面接実施率</t>
+        </is>
+      </c>
+      <c r="C22" s="16">
+        <f>IFERROR(D14/D13,"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>面接実施 ÷ 面接設定</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>内定率</t>
+        </is>
+      </c>
+      <c r="C23" s="16">
+        <f>IFERROR(D15/D14,"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>内定 ÷ 面接実施</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>承諾率</t>
+        </is>
+      </c>
+      <c r="C24" s="16">
+        <f>IFERROR(D16/D15,"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>承諾 ÷ 内定</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>③  媒体別 実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
           <t>媒体</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>応募数</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>書類通過</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E27" s="11" t="inlineStr">
         <is>
           <t>面接設定</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>面接実施</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>内定</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H27" s="11" t="inlineStr">
         <is>
           <t>承諾</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="13" t="inlineStr">
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C22" s="14">
+      <c r="C28" s="18">
         <f>COUNTIF(応募者データ!$B$3:$B$502,"バイトル")</f>
         <v/>
       </c>
-      <c r="D22" s="14">
+      <c r="D28" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E22" s="14">
+      <c r="E28" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$K$3:$K$502,"面接調整中")+COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$K$3:$K$502,"面接日確定")+COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="F22" s="14">
+      <c r="F28" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G28" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$M$3:$M$502,"入社予定")+COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$M$3:$M$502,"採用辞退")+COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
-      <c r="H22" s="14">
+      <c r="H28" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"バイトル",応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="15" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>マイナビバイト</t>
         </is>
       </c>
-      <c r="C23" s="16">
+      <c r="C29" s="20">
         <f>COUNTIF(応募者データ!$B$3:$B$502,"マイナビバイト")</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="D29" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E23" s="16">
+      <c r="E29" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$K$3:$K$502,"面接調整中")+COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$K$3:$K$502,"面接日確定")+COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F29" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G29" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$M$3:$M$502,"入社予定")+COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$M$3:$M$502,"採用辞退")+COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H29" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"マイナビバイト",応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="13" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>ちゃんと</t>
         </is>
       </c>
-      <c r="C24" s="14">
+      <c r="C30" s="18">
         <f>COUNTIF(応募者データ!$B$3:$B$502,"ちゃんと")</f>
         <v/>
       </c>
-      <c r="D24" s="14">
+      <c r="D30" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E24" s="14">
+      <c r="E30" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$K$3:$K$502,"面接調整中")+COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$K$3:$K$502,"面接日確定")+COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="F24" s="14">
+      <c r="F30" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="G24" s="14">
+      <c r="G30" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$M$3:$M$502,"入社予定")+COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$M$3:$M$502,"採用辞退")+COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
-      <c r="H24" s="14">
+      <c r="H30" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"ちゃんと",応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="15" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>社員紹介</t>
         </is>
       </c>
-      <c r="C25" s="16">
+      <c r="C31" s="20">
         <f>COUNTIF(応募者データ!$B$3:$B$502,"社員紹介")</f>
         <v/>
       </c>
-      <c r="D25" s="16">
+      <c r="D31" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E25" s="16">
+      <c r="E31" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$K$3:$K$502,"面接調整中")+COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$K$3:$K$502,"面接日確定")+COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F31" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G31" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$M$3:$M$502,"入社予定")+COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$M$3:$M$502,"採用辞退")+COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H31" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"社員紹介",応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="13" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="C26" s="14">
+      <c r="C32" s="18">
         <f>COUNTIF(応募者データ!$B$3:$B$502,"HP")</f>
         <v/>
       </c>
-      <c r="D26" s="14">
+      <c r="D32" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E26" s="14">
+      <c r="E32" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$K$3:$K$502,"面接調整中")+COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$K$3:$K$502,"面接日確定")+COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="F26" s="14">
+      <c r="F32" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="G26" s="14">
+      <c r="G32" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$M$3:$M$502,"入社予定")+COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$M$3:$M$502,"採用辞退")+COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
-      <c r="H26" s="14">
+      <c r="H32" s="18">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"HP",応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="15" t="inlineStr">
+    <row r="33">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="C27" s="16">
+      <c r="C33" s="20">
         <f>COUNTIF(応募者データ!$B$3:$B$502,"その他")</f>
         <v/>
       </c>
-      <c r="D27" s="16">
+      <c r="D33" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E27" s="16">
+      <c r="E33" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$K$3:$K$502,"面接調整中")+COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$K$3:$K$502,"面接日確定")+COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F33" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G33" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$M$3:$M$502,"入社予定")+COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$M$3:$M$502,"採用辞退")+COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
-      <c r="H27" s="16">
+      <c r="H33" s="20">
         <f>COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$B$3:$B$502,"その他",応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="17" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C28" s="18">
-        <f>SUM(C22:C27)</f>
-        <v/>
-      </c>
-      <c r="D28" s="18">
-        <f>SUM(D22:D27)</f>
-        <v/>
-      </c>
-      <c r="E28" s="18">
-        <f>SUM(E22:E27)</f>
-        <v/>
-      </c>
-      <c r="F28" s="18">
-        <f>SUM(F22:F27)</f>
-        <v/>
-      </c>
-      <c r="G28" s="18">
-        <f>SUM(G22:G27)</f>
-        <v/>
-      </c>
-      <c r="H28" s="18">
-        <f>SUM(H22:H27)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="C34" s="22">
+        <f>SUM(C28:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="22">
+        <f>SUM(D28:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="22">
+        <f>SUM(E28:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="22">
+        <f>SUM(F28:F33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="22">
+        <f>SUM(G28:G33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="22">
+        <f>SUM(H28:H33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>④  基地別 実績（NRT=成田 / CTS=千歳）</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="4" t="inlineStr">
+    <row r="37">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>基地</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C37" s="11" t="inlineStr">
         <is>
           <t>応募数</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D37" s="11" t="inlineStr">
         <is>
           <t>書類通過</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E37" s="11" t="inlineStr">
         <is>
           <t>面接設定</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F37" s="11" t="inlineStr">
         <is>
           <t>面接実施</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>内定</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H37" s="11" t="inlineStr">
         <is>
           <t>承諾</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="13" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>NRT（成田）</t>
         </is>
       </c>
-      <c r="C32" s="14">
+      <c r="C38" s="18">
         <f>COUNTIF(応募者データ!$C$3:$C$502,"NRT")</f>
         <v/>
       </c>
-      <c r="D32" s="14">
+      <c r="D38" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E32" s="14">
+      <c r="E38" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$K$3:$K$502,"面接調整中")+COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$K$3:$K$502,"面接日確定")+COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="F32" s="14">
+      <c r="F38" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="G32" s="14">
+      <c r="G38" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$M$3:$M$502,"入社予定")+COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$M$3:$M$502,"採用辞退")+COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
-      <c r="H32" s="14">
+      <c r="H38" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$C$3:$C$502,"NRT",応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="13" t="inlineStr">
+    <row r="39">
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>CTS（千歳）</t>
         </is>
       </c>
-      <c r="C33" s="14">
+      <c r="C39" s="18">
         <f>COUNTIF(応募者データ!$C$3:$C$502,"CTS")</f>
         <v/>
       </c>
-      <c r="D33" s="14">
+      <c r="D39" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
-      <c r="E33" s="14">
+      <c r="E39" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$K$3:$K$502,"面接調整中")+COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$K$3:$K$502,"面接日確定")+COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="F33" s="14">
+      <c r="F39" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
-      <c r="G33" s="14">
+      <c r="G39" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$M$3:$M$502,"入社予定")+COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$M$3:$M$502,"採用辞退")+COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
-      <c r="H33" s="14">
+      <c r="H39" s="18">
         <f>COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$M$3:$M$502,"採用")+COUNTIFS(応募者データ!$C$3:$C$502,"CTS",応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="B35" s="19" t="inlineStr">
+    <row r="41" ht="22" customHeight="1">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>⑤  拠点別 採用目標 達成状況（承諾＝採用人数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>拠点</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>採用目標</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>承諾実績</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>達成率</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>NRT（成田）</t>
+        </is>
+      </c>
+      <c r="C43" s="18">
+        <f>$D$5</f>
+        <v/>
+      </c>
+      <c r="D43" s="18">
+        <f>H38</f>
+        <v/>
+      </c>
+      <c r="E43" s="14">
+        <f>IFERROR(H38/$D$5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>CTS（千歳）</t>
+        </is>
+      </c>
+      <c r="C44" s="18">
+        <f>$F$5</f>
+        <v/>
+      </c>
+      <c r="D44" s="18">
+        <f>H39</f>
+        <v/>
+      </c>
+      <c r="E44" s="14">
+        <f>IFERROR(H39/$F$5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="21" t="inlineStr">
+        <is>
+          <t>合計</t>
+        </is>
+      </c>
+      <c r="C45" s="22">
+        <f>$H$5</f>
+        <v/>
+      </c>
+      <c r="D45" s="22">
+        <f>H38+H39</f>
+        <v/>
+      </c>
+      <c r="E45" s="23">
+        <f>IFERROR((H38+H39)/$H$5,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" s="24" t="inlineStr">
         <is>
           <t>◆ 凡例・定義</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>・黄色セル＝入力（目標値）。運用開始時に目標を設定してください（現在は仮値）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="20" t="inlineStr">
+    <row r="48">
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>・黄色セル＝入力。採用目標（NRT/CTSの承諾人数）と歩留まり前提を入れると、各段階の目標を自動で逆算します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>・目標列＝承諾目標から逆算（承諾20名→内定25→面接実施42→面接設定50→書類通過72→応募144）。歩留まりを変えれば再計算されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" s="25" t="inlineStr">
         <is>
           <t>・実績は［応募者データ］シートから自動集計。担当者は毎日そこを更新するだけです。</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="B38" s="20" t="inlineStr">
+    <row r="51">
+      <c r="B51" s="25" t="inlineStr">
         <is>
           <t>・前日／前日比は［日次レポート］の最終記録行との差分。毎日EODに1行追記してください。</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="20" t="inlineStr">
+    <row r="52">
+      <c r="B52" s="25" t="inlineStr">
         <is>
           <t>・面接設定＝面接ステータスが「面接調整中／面接日確定／面接実施済み」。面接実施＝「面接実施済み」。</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="B40" s="20" t="inlineStr">
+    <row r="53">
+      <c r="B53" s="25" t="inlineStr">
         <is>
           <t>・内定＝採用が「採用／入社予定／採用辞退／入社辞退」。承諾＝「採用／入社予定」。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="20">
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="D24:G24"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="D23:G23"/>
     <mergeCell ref="B36:H36"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B50:H50"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B41:H41"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="D20:G20"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="D22:G22"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B52:H52"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B48:H48"/>
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="D16:G16"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="B30:H30"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="D19:G19"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B53:H53"/>
   </mergeCells>
-  <conditionalFormatting sqref="E6:E11">
+  <conditionalFormatting sqref="E11:E16">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0">
       <formula>1</formula>
     </cfRule>
@@ -1957,12 +2168,24 @@
       <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G11">
+  <conditionalFormatting sqref="G11:G16">
     <cfRule type="cellIs" priority="4" operator="greaterThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
     <cfRule type="cellIs" priority="5" operator="lessThan" dxfId="3">
       <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E43:E45">
+    <cfRule type="cellIs" priority="6" operator="greaterThanOrEqual" dxfId="0">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="7" operator="between" dxfId="1">
+      <formula>0.7</formula>
+      <formula>0.9999</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="2">
+      <formula>0.7</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1991,344 +2214,344 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>マスタ（プルダウン用リスト）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="27" t="inlineStr">
         <is>
           <t>媒体</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="27" t="inlineStr">
         <is>
           <t>基地</t>
         </is>
       </c>
-      <c r="C2" s="22" t="inlineStr">
+      <c r="C2" s="27" t="inlineStr">
         <is>
           <t>性別</t>
         </is>
       </c>
-      <c r="D2" s="22" t="inlineStr">
+      <c r="D2" s="27" t="inlineStr">
         <is>
           <t>国籍</t>
         </is>
       </c>
-      <c r="E2" s="22" t="inlineStr">
+      <c r="E2" s="27" t="inlineStr">
         <is>
           <t>書類選考</t>
         </is>
       </c>
-      <c r="F2" s="22" t="inlineStr">
+      <c r="F2" s="27" t="inlineStr">
         <is>
           <t>書類NG理由</t>
         </is>
       </c>
-      <c r="G2" s="22" t="inlineStr">
+      <c r="G2" s="27" t="inlineStr">
         <is>
           <t>面接</t>
         </is>
       </c>
-      <c r="H2" s="22" t="inlineStr">
+      <c r="H2" s="27" t="inlineStr">
         <is>
           <t>面接NG理由</t>
         </is>
       </c>
-      <c r="I2" s="22" t="inlineStr">
+      <c r="I2" s="27" t="inlineStr">
         <is>
           <t>採用</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="28" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="28" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="28" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="28" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>未対応</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="28" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
+      <c r="G3" s="28" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="28" t="inlineStr">
         <is>
           <t>勤務条件不一致</t>
         </is>
       </c>
-      <c r="I3" s="23" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>マイナビバイト</t>
         </is>
       </c>
-      <c r="B4" s="23" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>CTS</t>
         </is>
       </c>
-      <c r="C4" s="23" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="D4" s="23" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>外国籍</t>
         </is>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="F4" s="23" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>通勤距離</t>
         </is>
       </c>
-      <c r="G4" s="23" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>面接調整中</t>
         </is>
       </c>
-      <c r="H4" s="23" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>シフト条件不一致</t>
         </is>
       </c>
-      <c r="I4" s="23" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>採用</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="28" t="inlineStr">
         <is>
           <t>ちゃんと</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>通過</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="28" t="inlineStr">
         <is>
           <t>国籍</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="28" t="inlineStr">
         <is>
           <t>面接日確定</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="28" t="inlineStr">
         <is>
           <t>経験不足</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="28" t="inlineStr">
         <is>
           <t>不採用</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>社員紹介</t>
         </is>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="28" t="inlineStr">
         <is>
           <t>日本語力</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="28" t="inlineStr">
         <is>
           <t>面接実施済み</t>
         </is>
       </c>
-      <c r="H6" s="23" t="inlineStr">
+      <c r="H6" s="28" t="inlineStr">
         <is>
           <t>接客適性</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t>採用辞退</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="28" t="inlineStr">
         <is>
           <t>HP</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>不通過</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="28" t="inlineStr">
         <is>
           <t>英語力</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="28" t="inlineStr">
         <is>
           <t>コミュニケーション</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="28" t="inlineStr">
         <is>
           <t>入社予定</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>辞退</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>勤務時間不一致</t>
         </is>
       </c>
-      <c r="H8" s="23" t="inlineStr">
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>日本語力</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>入社辞退</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>連絡不通</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="28" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="28" t="inlineStr">
         <is>
           <t>英語力</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="H10" s="23" t="inlineStr">
+      <c r="H10" s="28" t="inlineStr">
         <is>
           <t>航空保安上の要件</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="H11" s="23" t="inlineStr">
+      <c r="H11" s="28" t="inlineStr">
         <is>
           <t>通勤困難</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="H12" s="23" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>給与条件不一致</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="H13" s="23" t="inlineStr">
+      <c r="H13" s="28" t="inlineStr">
         <is>
           <t>入社可能時期が合わない</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="H14" s="23" t="inlineStr">
+      <c r="H14" s="28" t="inlineStr">
         <is>
           <t>他社内定</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="H15" s="23" t="inlineStr">
+      <c r="H15" s="28" t="inlineStr">
         <is>
           <t>本人辞退</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="H16" s="23" t="inlineStr">
+      <c r="H16" s="28" t="inlineStr">
         <is>
           <t>総合判断</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="H17" s="23" t="inlineStr">
+      <c r="H17" s="28" t="inlineStr">
         <is>
           <t>その他</t>
         </is>
@@ -2365,867 +2588,867 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>応募者データ（明細）　― 毎日ここを更新してください。ダッシュボードは自動集計されます ―</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>媒体</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>基地</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>応募日</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="22" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="22" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="22" t="inlineStr">
         <is>
           <t>性別</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="22" t="inlineStr">
         <is>
           <t>国籍</t>
         </is>
       </c>
-      <c r="I2" s="18" t="inlineStr">
+      <c r="I2" s="22" t="inlineStr">
         <is>
           <t>書類選考</t>
         </is>
       </c>
-      <c r="J2" s="18" t="inlineStr">
+      <c r="J2" s="22" t="inlineStr">
         <is>
           <t>書類NG理由</t>
         </is>
       </c>
-      <c r="K2" s="18" t="inlineStr">
+      <c r="K2" s="22" t="inlineStr">
         <is>
           <t>面接</t>
         </is>
       </c>
-      <c r="L2" s="18" t="inlineStr">
+      <c r="L2" s="22" t="inlineStr">
         <is>
           <t>面接NG理由</t>
         </is>
       </c>
-      <c r="M2" s="18" t="inlineStr">
+      <c r="M2" s="22" t="inlineStr">
         <is>
           <t>採用</t>
         </is>
       </c>
-      <c r="N2" s="18" t="inlineStr">
+      <c r="N2" s="22" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="n">
+      <c r="A3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D3" s="25" t="n">
+      <c r="D3" s="30" t="n">
         <v>46227</v>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="28" t="inlineStr">
         <is>
           <t>日高 秀光</t>
         </is>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="18" t="n">
         <v>73</v>
       </c>
-      <c r="G3" s="14" t="inlineStr">
+      <c r="G3" s="18" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="H3" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="18" t="inlineStr">
         <is>
           <t>不通過</t>
         </is>
       </c>
-      <c r="J3" s="23" t="inlineStr">
+      <c r="J3" s="28" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="K3" s="14" t="inlineStr">
+      <c r="K3" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L3" s="23" t="n"/>
-      <c r="M3" s="14" t="inlineStr">
+      <c r="L3" s="28" t="n"/>
+      <c r="M3" s="18" t="inlineStr">
         <is>
           <t>不採用</t>
         </is>
       </c>
-      <c r="N3" s="23" t="n"/>
+      <c r="N3" s="28" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n">
+      <c r="D4" s="30" t="n">
         <v>46230</v>
       </c>
-      <c r="E4" s="23" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>浅利 真弓</t>
         </is>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="18" t="n">
         <v>63</v>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="18" t="inlineStr">
         <is>
           <t>不通過</t>
         </is>
       </c>
-      <c r="J4" s="23" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L4" s="23" t="n"/>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="L4" s="28" t="n"/>
+      <c r="M4" s="18" t="inlineStr">
         <is>
           <t>不採用</t>
         </is>
       </c>
-      <c r="N4" s="23" t="n"/>
+      <c r="N4" s="28" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="n">
+      <c r="A5" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="30" t="n">
         <v>46231</v>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="28" t="inlineStr">
         <is>
           <t>浅木 洋二</t>
         </is>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="18" t="n">
         <v>76</v>
       </c>
-      <c r="G5" s="14" t="inlineStr">
+      <c r="G5" s="18" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>不通過</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="28" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L5" s="23" t="n"/>
-      <c r="M5" s="14" t="inlineStr">
+      <c r="L5" s="28" t="n"/>
+      <c r="M5" s="18" t="inlineStr">
         <is>
           <t>不採用</t>
         </is>
       </c>
-      <c r="N5" s="23" t="n"/>
+      <c r="N5" s="28" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="n">
+      <c r="A6" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="30" t="n">
         <v>46231</v>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="28" t="inlineStr">
         <is>
           <t>佐伯 幸男</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="18" t="n">
         <v>55</v>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>不通過</t>
         </is>
       </c>
-      <c r="J6" s="23" t="inlineStr">
+      <c r="J6" s="28" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L6" s="23" t="n"/>
-      <c r="M6" s="14" t="inlineStr">
+      <c r="L6" s="28" t="n"/>
+      <c r="M6" s="18" t="inlineStr">
         <is>
           <t>不採用</t>
         </is>
       </c>
-      <c r="N6" s="23" t="n"/>
+      <c r="N6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="30" t="n">
         <v>46232</v>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="28" t="inlineStr">
         <is>
           <t>町田 侑里夏</t>
         </is>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="18" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>通過</t>
         </is>
       </c>
-      <c r="J7" s="23" t="n"/>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="J7" s="28" t="n"/>
+      <c r="K7" s="18" t="inlineStr">
         <is>
           <t>面接調整中</t>
         </is>
       </c>
-      <c r="L7" s="23" t="n"/>
-      <c r="M7" s="14" t="inlineStr">
+      <c r="L7" s="28" t="n"/>
+      <c r="M7" s="18" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
-      <c r="N7" s="23" t="n"/>
+      <c r="N7" s="28" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="30" t="n">
         <v>46233</v>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>三木 祐樹</t>
         </is>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="18" t="n">
         <v>38</v>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>不通過</t>
         </is>
       </c>
-      <c r="J8" s="23" t="inlineStr">
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="K8" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L8" s="23" t="n"/>
-      <c r="M8" s="14" t="inlineStr">
+      <c r="L8" s="28" t="n"/>
+      <c r="M8" s="18" t="inlineStr">
         <is>
           <t>不採用</t>
         </is>
       </c>
-      <c r="N8" s="23" t="n"/>
+      <c r="N8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="30" t="n">
         <v>46233</v>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="28" t="inlineStr">
         <is>
           <t>金澤 拓也</t>
         </is>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="18" t="n">
         <v>19</v>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="18" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>通過</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="14" t="inlineStr">
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="18" t="inlineStr">
         <is>
           <t>面接調整中</t>
         </is>
       </c>
-      <c r="L9" s="23" t="n"/>
-      <c r="M9" s="14" t="inlineStr">
+      <c r="L9" s="28" t="n"/>
+      <c r="M9" s="18" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
-      <c r="N9" s="23" t="n"/>
+      <c r="N9" s="28" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="18" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="30" t="n">
         <v>46233</v>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="28" t="inlineStr">
         <is>
           <t>NGUYEN NGOC DINH</t>
         </is>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="18" t="n">
         <v>25</v>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>外国籍</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>不通過</t>
         </is>
       </c>
-      <c r="J10" s="23" t="inlineStr">
+      <c r="J10" s="28" t="inlineStr">
         <is>
           <t>日本語力</t>
         </is>
       </c>
-      <c r="K10" s="14" t="inlineStr">
+      <c r="K10" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L10" s="23" t="n"/>
-      <c r="M10" s="14" t="inlineStr">
+      <c r="L10" s="28" t="n"/>
+      <c r="M10" s="18" t="inlineStr">
         <is>
           <t>不採用</t>
         </is>
       </c>
-      <c r="N10" s="23" t="inlineStr">
+      <c r="N10" s="28" t="inlineStr">
         <is>
           <t>N3</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="18" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="30" t="n">
         <v>46236</v>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="28" t="inlineStr">
         <is>
           <t>Hashini Navodya</t>
         </is>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="18" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="H11" s="18" t="inlineStr">
         <is>
           <t>外国籍</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="18" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n"/>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L11" s="23" t="n"/>
-      <c r="M11" s="14" t="inlineStr">
+      <c r="L11" s="28" t="n"/>
+      <c r="M11" s="18" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
-      <c r="N11" s="23" t="n"/>
+      <c r="N11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="18" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="30" t="n">
         <v>46236</v>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>JARGALBAYAR ENKHBAYAN</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>外国籍</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="J12" s="23" t="n"/>
-      <c r="K12" s="14" t="inlineStr">
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L12" s="23" t="n"/>
-      <c r="M12" s="14" t="inlineStr">
+      <c r="L12" s="28" t="n"/>
+      <c r="M12" s="18" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
-      <c r="N12" s="23" t="n"/>
+      <c r="N12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="n">
+      <c r="A13" s="18" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>NRT</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="30" t="n">
         <v>46237</v>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>坂本 隼斗</t>
         </is>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="18" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="H13" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="18" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="J13" s="23" t="n"/>
-      <c r="K13" s="14" t="inlineStr">
+      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L13" s="23" t="n"/>
-      <c r="M13" s="14" t="inlineStr">
+      <c r="L13" s="28" t="n"/>
+      <c r="M13" s="18" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
-      <c r="N13" s="23" t="n"/>
+      <c r="N13" s="28" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="18" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>バイトル</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>CTS</t>
         </is>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="30" t="n">
         <v>46236</v>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="28" t="inlineStr">
         <is>
           <t>Hashini Navodya</t>
         </is>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="18" t="n">
         <v>21</v>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>外国籍</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="J14" s="23" t="n"/>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L14" s="23" t="n"/>
-      <c r="M14" s="14" t="inlineStr">
+      <c r="L14" s="28" t="n"/>
+      <c r="M14" s="18" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
-      <c r="N14" s="23" t="n"/>
+      <c r="N14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="18" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>マイナビバイト</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>CTS</t>
         </is>
       </c>
-      <c r="D15" s="25" t="n">
+      <c r="D15" s="30" t="n">
         <v>46233</v>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="28" t="inlineStr">
         <is>
           <t>竹内 愛</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="18" t="n">
         <v>33</v>
       </c>
-      <c r="G15" s="14" t="inlineStr">
+      <c r="G15" s="18" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="H15" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="I15" s="18" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="J15" s="23" t="n"/>
-      <c r="K15" s="14" t="inlineStr">
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L15" s="23" t="n"/>
-      <c r="M15" s="14" t="inlineStr">
+      <c r="L15" s="28" t="n"/>
+      <c r="M15" s="18" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
-      <c r="N15" s="23" t="n"/>
+      <c r="N15" s="28" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="n">
+      <c r="A16" s="18" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>マイナビバイト</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>CTS</t>
         </is>
       </c>
-      <c r="D16" s="25" t="n">
+      <c r="D16" s="30" t="n">
         <v>46233</v>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="28" t="inlineStr">
         <is>
           <t>高砂 琴音</t>
         </is>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="18" t="n">
         <v>18</v>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>日本</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>確認中</t>
         </is>
       </c>
-      <c r="J16" s="23" t="n"/>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="18" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
-      <c r="L16" s="23" t="n"/>
-      <c r="M16" s="14" t="inlineStr">
+      <c r="L16" s="28" t="n"/>
+      <c r="M16" s="18" t="inlineStr">
         <is>
           <t>選考中</t>
         </is>
       </c>
-      <c r="N16" s="23" t="inlineStr">
+      <c r="N16" s="28" t="inlineStr">
         <is>
           <t>高校生だが外航のGATE経験者の可能性あり</t>
         </is>
@@ -3291,435 +3514,435 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>日次レポート（毎日 EOD に担当者が1行追記）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="31" t="inlineStr">
         <is>
           <t>使い方：応募者データを更新後、当日の累計値を下表に1行追記します（右の「現在の累計値」を転記でOK）。ダッシュボードの前日比・推移グラフに自動反映されます。灰色の行はサンプルです。実データ入力時に削除してください。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>応募数</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>書類通過</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>面接設定</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>面接実施</t>
         </is>
       </c>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>内定</t>
         </is>
       </c>
-      <c r="G3" s="18" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t>承諾</t>
         </is>
       </c>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>担当者</t>
         </is>
       </c>
-      <c r="I3" s="18" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="K3" s="27" t="inlineStr">
+      <c r="K3" s="32" t="inlineStr">
         <is>
           <t>現在の累計値（自動）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="n">
+      <c r="A4" s="33" t="n">
         <v>46234</v>
       </c>
-      <c r="B4" s="29" t="n">
+      <c r="B4" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="29" t="n">
+      <c r="D4" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="29" t="n">
+      <c r="F4" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="29" t="n">
+      <c r="G4" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="30" t="inlineStr">
+      <c r="H4" s="35" t="inlineStr">
         <is>
           <t>（サンプル）</t>
         </is>
       </c>
-      <c r="I4" s="30" t="inlineStr">
+      <c r="I4" s="35" t="inlineStr">
         <is>
           <t>← サンプル：削除して実データを入力</t>
         </is>
       </c>
-      <c r="K4" s="31" t="inlineStr">
+      <c r="K4" s="36" t="inlineStr">
         <is>
           <t>応募数</t>
         </is>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="18">
         <f>COUNTA(応募者データ!$E$3:$E$502)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n">
+      <c r="A5" s="33" t="n">
         <v>46235</v>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="29" t="n">
+      <c r="G5" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="30" t="inlineStr">
+      <c r="H5" s="35" t="inlineStr">
         <is>
           <t>（サンプル）</t>
         </is>
       </c>
-      <c r="I5" s="30" t="inlineStr"/>
-      <c r="K5" s="31" t="inlineStr">
+      <c r="I5" s="35" t="inlineStr"/>
+      <c r="K5" s="36" t="inlineStr">
         <is>
           <t>書類通過</t>
         </is>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="18">
         <f>COUNTIF(応募者データ!$I$3:$I$502,"通過")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="n">
+      <c r="A6" s="33" t="n">
         <v>46236</v>
       </c>
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="29" t="n">
+      <c r="G6" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="30" t="inlineStr">
+      <c r="H6" s="35" t="inlineStr">
         <is>
           <t>（サンプル）</t>
         </is>
       </c>
-      <c r="I6" s="30" t="inlineStr"/>
-      <c r="K6" s="31" t="inlineStr">
+      <c r="I6" s="35" t="inlineStr"/>
+      <c r="K6" s="36" t="inlineStr">
         <is>
           <t>面接設定</t>
         </is>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="18">
         <f>COUNTIF(応募者データ!$K$3:$K$502,"面接調整中")+COUNTIF(応募者データ!$K$3:$K$502,"面接日確定")+COUNTIF(応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="32" t="n"/>
-      <c r="B7" s="12" t="n"/>
-      <c r="C7" s="12" t="n"/>
-      <c r="D7" s="12" t="n"/>
-      <c r="E7" s="12" t="n"/>
-      <c r="F7" s="12" t="n"/>
-      <c r="G7" s="12" t="n"/>
-      <c r="H7" s="12" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="K7" s="31" t="inlineStr">
+      <c r="A7" s="37" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="K7" s="36" t="inlineStr">
         <is>
           <t>面接実施</t>
         </is>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="18">
         <f>COUNTIF(応募者データ!$K$3:$K$502,"面接実施済み")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="n"/>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="K8" s="31" t="inlineStr">
+      <c r="A8" s="37" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
+      <c r="G8" s="17" t="n"/>
+      <c r="H8" s="17" t="n"/>
+      <c r="I8" s="17" t="n"/>
+      <c r="K8" s="36" t="inlineStr">
         <is>
           <t>内定</t>
         </is>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="18">
         <f>COUNTIF(応募者データ!$M$3:$M$502,"採用")+COUNTIF(応募者データ!$M$3:$M$502,"入社予定")+COUNTIF(応募者データ!$M$3:$M$502,"採用辞退")+COUNTIF(応募者データ!$M$3:$M$502,"入社辞退")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="32" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="K9" s="31" t="inlineStr">
+      <c r="A9" s="37" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="17" t="n"/>
+      <c r="G9" s="17" t="n"/>
+      <c r="H9" s="17" t="n"/>
+      <c r="I9" s="17" t="n"/>
+      <c r="K9" s="36" t="inlineStr">
         <is>
           <t>承諾</t>
         </is>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="18">
         <f>COUNTIF(応募者データ!$M$3:$M$502,"採用")+COUNTIF(応募者データ!$M$3:$M$502,"入社予定")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="n"/>
-      <c r="B10" s="12" t="n"/>
-      <c r="C10" s="12" t="n"/>
-      <c r="D10" s="12" t="n"/>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="12" t="n"/>
-      <c r="G10" s="12" t="n"/>
-      <c r="H10" s="12" t="n"/>
-      <c r="I10" s="12" t="n"/>
+      <c r="A10" s="37" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+      <c r="G10" s="17" t="n"/>
+      <c r="H10" s="17" t="n"/>
+      <c r="I10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="32" t="n"/>
-      <c r="B11" s="12" t="n"/>
-      <c r="C11" s="12" t="n"/>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="12" t="n"/>
-      <c r="G11" s="12" t="n"/>
-      <c r="H11" s="12" t="n"/>
-      <c r="I11" s="12" t="n"/>
+      <c r="A11" s="37" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="17" t="n"/>
+      <c r="G11" s="17" t="n"/>
+      <c r="H11" s="17" t="n"/>
+      <c r="I11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
+      <c r="A12" s="37" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
+      <c r="G12" s="17" t="n"/>
+      <c r="H12" s="17" t="n"/>
+      <c r="I12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
+      <c r="A13" s="37" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
+      <c r="G13" s="17" t="n"/>
+      <c r="H13" s="17" t="n"/>
+      <c r="I13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
+      <c r="A14" s="37" t="n"/>
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="17" t="n"/>
+      <c r="G14" s="17" t="n"/>
+      <c r="H14" s="17" t="n"/>
+      <c r="I14" s="17" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
+      <c r="A15" s="37" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
+      <c r="A16" s="37" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="17" t="n"/>
+      <c r="H16" s="17" t="n"/>
+      <c r="I16" s="17" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
+      <c r="A17" s="37" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="17" t="n"/>
+      <c r="H17" s="17" t="n"/>
+      <c r="I17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="32" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
+      <c r="A18" s="37" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="32" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
+      <c r="A19" s="37" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="32" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
+      <c r="A20" s="37" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="17" t="n"/>
+      <c r="H20" s="17" t="n"/>
+      <c r="I20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="32" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
+      <c r="A21" s="37" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="17" t="n"/>
+      <c r="H21" s="17" t="n"/>
+      <c r="I21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="32" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
+      <c r="A22" s="37" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="17" t="n"/>
+      <c r="H22" s="17" t="n"/>
+      <c r="I22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
+      <c r="A23" s="37" t="n"/>
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="17" t="n"/>
+      <c r="H23" s="17" t="n"/>
+      <c r="I23" s="17" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="32" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
+      <c r="A24" s="37" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="17" t="n"/>
+      <c r="H24" s="17" t="n"/>
+      <c r="I24" s="17" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="32" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
+      <c r="A25" s="37" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="32" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
+      <c r="A26" s="37" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="17" t="n"/>
+      <c r="H26" s="17" t="n"/>
+      <c r="I26" s="17" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/短時間勤務者_採用KPIダッシュボード.xlsx
+++ b/短時間勤務者_採用KPIダッシュボード.xlsx
@@ -554,7 +554,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>採用ファネル（実績）</a:t>
+              <a:t>採用ファネル（実績・人）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -595,9 +595,26 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -606,8 +623,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>人数</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -631,7 +663,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>媒体別 応募数</a:t>
+              <a:t>媒体別 応募数（人）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -677,9 +709,26 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>媒体</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -688,8 +737,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>人数</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -713,7 +777,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>推移（日次）</a:t>
+              <a:t>採用ファネル 日次推移（累計・人）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -745,12 +809,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'日次レポート'!$A$4:$A$16</f>
+              <f>'日次レポート'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'日次レポート'!$B$4:$B$16</f>
+              <f>'日次レポート'!$B$4:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -777,12 +841,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'日次レポート'!$A$4:$A$16</f>
+              <f>'日次レポート'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'日次レポート'!$C$4:$C$16</f>
+              <f>'日次レポート'!$C$4:$C$13</f>
             </numRef>
           </val>
         </ser>
@@ -809,12 +873,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'日次レポート'!$A$4:$A$16</f>
+              <f>'日次レポート'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'日次レポート'!$D$4:$D$16</f>
+              <f>'日次レポート'!$D$4:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -841,12 +905,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'日次レポート'!$A$4:$A$16</f>
+              <f>'日次レポート'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'日次レポート'!$E$4:$E$16</f>
+              <f>'日次レポート'!$E$4:$E$13</f>
             </numRef>
           </val>
         </ser>
@@ -873,12 +937,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'日次レポート'!$A$4:$A$16</f>
+              <f>'日次レポート'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'日次レポート'!$F$4:$F$16</f>
+              <f>'日次レポート'!$F$4:$F$13</f>
             </numRef>
           </val>
         </ser>
@@ -905,12 +969,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'日次レポート'!$A$4:$A$16</f>
+              <f>'日次レポート'!$A$4:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'日次レポート'!$G$4:$G$16</f>
+              <f>'日次レポート'!$G$4:$G$13</f>
             </numRef>
           </val>
         </ser>
@@ -922,9 +986,27 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日付</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <numFmt formatCode="m/d" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -933,15 +1015,30 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>人数（累計）</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -961,7 +1058,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>年齢分布</a:t>
+              <a:t>年齢分布（人）</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1002,9 +1099,26 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>年齢層</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
       </catAx>
@@ -1013,8 +1127,23 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
-        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>人数</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
@@ -1079,7 +1208,7 @@
       <row>35</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4320000" cy="2520000"/>
+    <ext cx="4680000" cy="2880000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
